--- a/LISTA BOMBEROS CDELU 2025 - CONSOLIDADO.xlsx
+++ b/LISTA BOMBEROS CDELU 2025 - CONSOLIDADO.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="11_56113DA8955F782EE27B58764C5DCE3AC7CAFF16" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1815" yWindow="1815" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CONSOLIDADO" sheetId="1" r:id="rId1"/>
